--- a/youtube/虎の巻_youtube.xlsx
+++ b/youtube/虎の巻_youtube.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１９.副業＿youtube\youtube\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業２\youtube\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE49434-9FB7-4153-94D9-4BDB4C7778BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAA7974-B060-4B51-81D2-FED0D2FAF647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5D72FD83-ED66-4A9F-9BCE-E519E2572B6D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Canvaで口が動くアニメーションを作る方法！イラストを喋らせます</t>
     <phoneticPr fontId="1"/>
@@ -222,6 +222,36 @@
   </si>
   <si>
     <t>■Youtube</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/channel/UCzgvsvl6xKRdxwHAcdXiIGw</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青いクローバー</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>picky.big2025@gmail.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■shotcut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>映像モード</t>
+    <rPh sb="0" eb="2">
+      <t>エイゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HD 1080p 30 fps</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -695,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485A8FF1-FC7D-4AB4-9F06-D999F003FDA7}">
-  <dimension ref="B3:E45"/>
+  <dimension ref="B3:F50"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.7">
@@ -743,32 +773,32 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B33" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B37" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B38" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
@@ -776,24 +806,48 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B42" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.7">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B44" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.7">
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B45" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.7">
+      <c r="B47" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -801,8 +855,10 @@
   <hyperlinks>
     <hyperlink ref="B30" r:id="rId1" xr:uid="{E73B06F1-203E-4A55-B284-4892618C3142}"/>
     <hyperlink ref="B45" r:id="rId2" xr:uid="{4C8C8F50-F3A0-40AF-BF6C-2B6D14D4892D}"/>
+    <hyperlink ref="B47" r:id="rId3" xr:uid="{1D5D0352-FBC0-468E-9446-47AE6275B3BD}"/>
+    <hyperlink ref="F44" r:id="rId4" xr:uid="{48C4CE8A-9C3B-43F1-883C-86074798626A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/youtube/虎の巻_youtube.xlsx
+++ b/youtube/虎の巻_youtube.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業２\youtube\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAA7974-B060-4B51-81D2-FED0D2FAF647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C74BC03-7EBB-4B24-844B-0F8680329C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5D72FD83-ED66-4A9F-9BCE-E519E2572B6D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Canvaで口が動くアニメーションを作る方法！イラストを喋らせます</t>
     <phoneticPr fontId="1"/>
@@ -252,6 +252,71 @@
   </si>
   <si>
     <t>HD 1080p 30 fps</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■チャンネルのコンテンツ（リスト）の作り方</t>
+    <rPh sb="18" eb="19">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Youtube Studioをクリック（左メニュー）→コンテンツ（左メニュー）→再生リスト（メニュー）→右上のボタン・作成→新しい再生リスト</t>
+    <rPh sb="20" eb="21">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ミギウエ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■公開はカスタマイズ（左メニュー）→ホーム（メニュー）から</t>
+    <rPh sb="1" eb="3">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■動画追加</t>
+    <rPh sb="1" eb="3">
+      <t>ドウガ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Youtubeスタジオ→カスタマイズ→作成した再生リストをクリック</t>
+    <rPh sb="19" eb="21">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サイセイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -725,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485A8FF1-FC7D-4AB4-9F06-D999F003FDA7}">
-  <dimension ref="B3:F50"/>
+  <dimension ref="B3:F58"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.7">
@@ -848,6 +913,31 @@
       </c>
       <c r="D50" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C58" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/youtube/虎の巻_youtube.xlsx
+++ b/youtube/虎の巻_youtube.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業２\youtube\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C74BC03-7EBB-4B24-844B-0F8680329C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA524CE-B085-4645-8EFA-3ED268CC8B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5D72FD83-ED66-4A9F-9BCE-E519E2572B6D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Canvaで口が動くアニメーションを作る方法！イラストを喋らせます</t>
     <phoneticPr fontId="1"/>
@@ -319,12 +319,129 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>■ショートについて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TickTok、Instagram、Xに投稿すると効果がある</t>
+    <rPh sb="20" eb="22">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ショートサイズと同じでよい</t>
+    <rPh sb="8" eb="9">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TickTok</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Instagram</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手順:</t>
+  </si>
+  <si>
+    <t>1. YouTubeで動画のURLをコピーする。</t>
+  </si>
+  <si>
+    <t>2. インスタでストーリーズ作成画面を開く（または投稿したリールから「ストーリーズに追加」を選ぶ）。</t>
+  </si>
+  <si>
+    <t>3. 画面上の「スタンプアイコン（顔のマーク）」をタップし、**「リンク」**を選択。</t>
+  </si>
+  <si>
+    <t>4. URLを貼り付け、「スタンプテキストをカスタマイズ」で「動画を見る！」などと入力して配置する。</t>
+  </si>
+  <si>
+    <r>
+      <t>コツ:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 「続きはここから」などの文字や動く矢印を添えると、クリック率が上がります。</t>
+    </r>
+  </si>
+  <si>
+    <t>□Youtubeへの誘導の仕方</t>
+    <rPh sb="10" eb="12">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シカタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. 【基本】動画を「直接」アップして、リプライ欄にリンク</t>
+  </si>
+  <si>
+    <t>Xの本文にYouTubeのURLを貼ると、X側が「ユーザーを自分のサイトから逃したくない」と判断し、表示回数を制限することがあります。</t>
+  </si>
+  <si>
+    <r>
+      <t>手順：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1. まず、動画ファイル（mp4など）を直接アップロードして投稿します。 2. その投稿の**「返信（リプライ）欄」**に、「続きやフルバージョンはこちらから！」とYouTubeのリンクを貼ります。</t>
+    </r>
+  </si>
+  <si>
+    <t>メリット：メインの投稿の表示回数を落とさずに、興味を持った人だけをスムーズにYouTubeへ誘導できます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>和美：pick.big2026@gmail.com</t>
+    <rPh sb="0" eb="2">
+      <t>カズミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「続きは YouTube にあるよ。プロフィールの名前で検索してね」</t>
+  </si>
+  <si>
+    <t>プロフィール名（ID）をYouTube</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +484,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -393,7 +519,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -405,6 +531,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -790,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485A8FF1-FC7D-4AB4-9F06-D999F003FDA7}">
-  <dimension ref="B3:F58"/>
+  <dimension ref="B3:I78"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.7">
@@ -938,6 +1076,116 @@
     <row r="58" spans="2:4" x14ac:dyDescent="0.7">
       <c r="C58" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="B60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.7">
+      <c r="C64" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C65" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D65" t="s">
+        <v>33</v>
+      </c>
+      <c r="I65" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="E67" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C68" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C69" s="7"/>
+      <c r="E69" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C70" s="7"/>
+      <c r="E70" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C71" s="7"/>
+      <c r="E71" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C72" s="7"/>
+      <c r="E72" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C73" s="7"/>
+      <c r="E73" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="C74" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="E75" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="76" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="E76" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="77" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="E77" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="3:9" x14ac:dyDescent="0.7">
+      <c r="E78" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/youtube/虎の巻_youtube.xlsx
+++ b/youtube/虎の巻_youtube.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業２\youtube\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA524CE-B085-4645-8EFA-3ED268CC8B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF60EC-DB31-4CD0-93F6-1A6DA0B55A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5D72FD83-ED66-4A9F-9BCE-E519E2572B6D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>Canvaで口が動くアニメーションを作る方法！イラストを喋らせます</t>
     <phoneticPr fontId="1"/>
@@ -435,6 +435,14 @@
   </si>
   <si>
     <t>プロフィール名（ID）をYouTube</t>
+  </si>
+  <si>
+    <t>blueクローバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>picky.big2026@gmail.com</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -976,32 +984,32 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B33" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B37" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B38" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
@@ -1009,33 +1017,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B42" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B44" t="s">
         <v>18</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>20</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.7">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B45" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.7">
+      <c r="F45" t="s">
+        <v>51</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.7">
       <c r="B47" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,9 +1208,10 @@
     <hyperlink ref="B30" r:id="rId1" xr:uid="{E73B06F1-203E-4A55-B284-4892618C3142}"/>
     <hyperlink ref="B45" r:id="rId2" xr:uid="{4C8C8F50-F3A0-40AF-BF6C-2B6D14D4892D}"/>
     <hyperlink ref="B47" r:id="rId3" xr:uid="{1D5D0352-FBC0-468E-9446-47AE6275B3BD}"/>
-    <hyperlink ref="F44" r:id="rId4" xr:uid="{48C4CE8A-9C3B-43F1-883C-86074798626A}"/>
+    <hyperlink ref="H44" r:id="rId4" xr:uid="{48C4CE8A-9C3B-43F1-883C-86074798626A}"/>
+    <hyperlink ref="H45" r:id="rId5" xr:uid="{8B62F7A3-46FB-4593-B736-101C68E9097A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>